--- a/ig/DM_FINESS_New/ValueSet-jdv-j372-convention-rass.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j372-convention-rass.xlsx
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs RASS contenant les engagements de type Convention.</t>
+    <t>Liste des engagements de type Convention pour le RASS</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j372-convention-rass.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j372-convention-rass.xlsx
@@ -30,7 +30,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.6.1.377</t>
+    <t>OID:1.2.250.1.213.1.6.1.386</t>
   </si>
   <si>
     <t>Version</t>
